--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
   <si>
     <t>Filename</t>
   </si>
@@ -808,676 +808,691 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9865,0.0051,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9852,0.0006,0.0003,0.0069</t>
-  </si>
-  <si>
-    <t>0.0231,0.0007,0.0001,0.9933</t>
+    <t>0.9447,0.0047,0.0023,0.0152</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9695,0.0021,0.0002,0.0094</t>
+  </si>
+  <si>
+    <t>0.0036,0.0022,0.0001,0.9983</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1140,0.0002,0.9141,0.0002</t>
+  </si>
+  <si>
+    <t>0.9021,0.0001,0.1804,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.9949,0.0006</t>
+  </si>
+  <si>
+    <t>0.9943,0.0001,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9968,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0416,0.0012,0.9501,0.0004</t>
+  </si>
+  <si>
+    <t>0.9838,0.0001,0.0160,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0036,0.9835,0.0004</t>
+  </si>
+  <si>
+    <t>0.1041,0.0000,0.9498,0.0000</t>
+  </si>
+  <si>
+    <t>0.0063,0.0001,0.9903,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0189,0.9862,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9527,0.0360,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9998,0.0354</t>
+  </si>
+  <si>
+    <t>0.0020,0.9932,0.0055,0.0000</t>
+  </si>
+  <si>
+    <t>0.9919,0.0063,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9265,0.0023,0.0350,0.0008</t>
+  </si>
+  <si>
+    <t>0.2891,0.7358,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9961,0.0702,0.0001</t>
+  </si>
+  <si>
+    <t>0.0334,0.0034,0.9343,0.0022</t>
+  </si>
+  <si>
+    <t>0.0064,0.0007,0.9911,0.0015</t>
+  </si>
+  <si>
+    <t>0.1142,0.0054,0.8383,0.0010</t>
+  </si>
+  <si>
+    <t>0.0075,0.0001,0.9870,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0109,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.0001,0.0534</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0453,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9987,0.0008</t>
+  </si>
+  <si>
+    <t>0.9825,0.0228,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0118</t>
+  </si>
+  <si>
+    <t>0.9946,0.0036,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.7289,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0047,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0004,0.9925,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9655,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9979,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.7529,0.0107,0.1077,0.0024</t>
+  </si>
+  <si>
+    <t>0.0181,0.0006,0.9763,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.9806,0.9893,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9037,0.9864,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0081,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9876,0.9722,0.0000</t>
+  </si>
+  <si>
+    <t>0.0096,0.0001,0.0028,0.9924</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0005,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0006,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9724,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9350,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9302,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9767,0.9447,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.8835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9944,0.9731,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0038,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0023,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9839,0.0004,0.0107,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0002,0.9965,0.0009</t>
-  </si>
-  <si>
-    <t>0.6520,0.0012,0.4179,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0004,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.9958,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9992,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0503,0.0033,0.9243,0.0031</t>
-  </si>
-  <si>
-    <t>0.9982,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0101,0.0001,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0008,0.9947,0.0005</t>
-  </si>
-  <si>
-    <t>0.0714,0.0001,0.9636,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0000,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9990,0.0051</t>
-  </si>
-  <si>
-    <t>0.0130,0.9891,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9810,0.0144,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9994,0.0460</t>
-  </si>
-  <si>
-    <t>0.0028,0.9869,0.0131,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0019,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0052,0.9937,0.0026</t>
-  </si>
-  <si>
-    <t>0.0744,0.9288,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9973,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0496,0.8631,0.0031</t>
-  </si>
-  <si>
-    <t>0.0072,0.0016,0.9904,0.0007</t>
-  </si>
-  <si>
-    <t>0.0103,0.0150,0.9679,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0018,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9918,0.0002,0.3054</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0073,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0001</t>
+    <t>0.9988,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0009,0.9973,0.0006</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9998,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.0004,0.9990,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0028,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0027,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9935,0.0055,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9992,0.0433</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.9799,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9938,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9983,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9929,0.0001,0.0074,0.0000</t>
-  </si>
-  <si>
-    <t>0.7215,0.0131,0.1188,0.0018</t>
-  </si>
-  <si>
-    <t>0.0040,0.0029,0.9926,0.0035</t>
-  </si>
-  <si>
-    <t>0.0000,0.9598,0.9927,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9134,0.7350,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9946,0.9319,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.0001,0.0023,0.9951</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9941,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9949,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9850,0.9662,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9788,0.8751,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9672,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9875,0.1210,0.0000</t>
+    <t>0.0006,0.9991,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.9843,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.0021,0.9950,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.8890,0.1613,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.7921,0.0099,0.0463,0.0108</t>
+  </si>
+  <si>
+    <t>0.9728,0.0003,0.0287,0.0001</t>
+  </si>
+  <si>
+    <t>0.7614,0.0830,0.0243,0.0020</t>
+  </si>
+  <si>
+    <t>0.9640,0.0059,0.0111,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0062,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9983,0.0966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.9958,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9719,0.0198,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9358,0.0709,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0028,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.9966,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.9878,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.9971,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6507,0.3490,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0001,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.7070,0.0002,0.4164,0.0000</t>
-  </si>
-  <si>
-    <t>0.9442,0.0119,0.0138,0.0006</t>
-  </si>
-  <si>
-    <t>0.5971,0.0032,0.3337,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.0136,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9623,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9531,0.0268,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.8268,0.2261,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.2519,0.9667,0.0008</t>
-  </si>
-  <si>
-    <t>0.0082,0.0232,0.9732,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0042,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.9910,0.0032,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0104,0.0000,0.9872,0.0005</t>
-  </si>
-  <si>
-    <t>0.9187,0.0007,0.0832,0.0007</t>
-  </si>
-  <si>
-    <t>0.0159,0.0001,0.0000,0.9941</t>
-  </si>
-  <si>
-    <t>0.0001,0.9527,0.9834,0.0001</t>
-  </si>
-  <si>
-    <t>0.0572,0.8110,0.0285,0.0084</t>
-  </si>
-  <si>
-    <t>0.1643,0.8236,0.0058,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1987,0.0001,0.0014,0.8807</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0215,0.9955,0.0429</t>
-  </si>
-  <si>
-    <t>0.9725,0.0001,0.0060,0.0101</t>
-  </si>
-  <si>
-    <t>0.9274,0.0006,0.0447,0.0019</t>
-  </si>
-  <si>
-    <t>0.3606,0.6460,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0011,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0060,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9639,0.0176,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0002,0.0000</t>
+    <t>0.0000,0.9970,0.8977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.5139,0.7424,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9451,0.0025,0.0293,0.0005</t>
+  </si>
+  <si>
+    <t>0.7589,0.0000,0.3596,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0005,0.0001,0.9981</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9448,0.6808,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9948,0.0006,0.0057</t>
+  </si>
+  <si>
+    <t>0.0826,0.8990,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7559,0.0001,0.0067,0.1823</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0062,0.9955,0.0287</t>
+  </si>
+  <si>
+    <t>0.9744,0.0000,0.0015,0.0190</t>
+  </si>
+  <si>
+    <t>0.9368,0.0005,0.0306,0.0021</t>
+  </si>
+  <si>
+    <t>0.0461,0.9049,0.0130,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8253,0.0918,0.0055,0.0011</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8990,0.1293,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0022,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0022,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.6008,0.2278,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.2544,0.7933,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.2222,0.8463,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7170,0.1654,0.0339,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0038,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9979,0.0006,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0013,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9785,0.0103,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.5260,0.5836,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.8811,0.2095,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8561,0.0063,0.1045,0.0004</t>
-  </si>
-  <si>
-    <t>0.9704,0.0313,0.0012,0.0003</t>
+    <t>0.9690,0.0365,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0026,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0132,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.1007,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0005,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9982,0.0008</t>
+  </si>
+  <si>
+    <t>0.4768,0.0011,0.5910,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.0028,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0013,0.9934,0.0007</t>
+  </si>
+  <si>
+    <t>0.0600,0.0449,0.8310,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.6088,0.6955,0.0023</t>
+  </si>
+  <si>
+    <t>0.0338,0.0030,0.9719,0.0004</t>
+  </si>
+  <si>
+    <t>0.7544,0.0040,0.1927,0.0005</t>
+  </si>
+  <si>
+    <t>0.1400,0.0158,0.7600,0.0039</t>
+  </si>
+  <si>
+    <t>0.0086,0.9923,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9979,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9723,0.0426,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8973,0.1222,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.3771,0.7384,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9110,0.0165,0.0235,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9596,0.0013,0.0105,0.0055</t>
+  </si>
+  <si>
+    <t>0.6149,0.0090,0.3564,0.0014</t>
+  </si>
+  <si>
+    <t>0.0451,0.0001,0.9544,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0053</t>
+  </si>
+  <si>
+    <t>0.0312,0.0583,0.7598,0.0034</t>
+  </si>
+  <si>
+    <t>0.0007,0.0446,0.9958,0.0003</t>
+  </si>
+  <si>
+    <t>0.1551,0.0003,0.9046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.5773,0.5043,0.0031</t>
   </si>
   <si>
     <t>0.9983,0.0008,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9959,0.0035,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9462,0.0632,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0007,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0024,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.1173,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9996,0.0000</t>
+    <t>0.9751,0.0270,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0044,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0012,0.9979,0.0031</t>
+  </si>
+  <si>
+    <t>0.8064,0.0165,0.0758,0.0044</t>
+  </si>
+  <si>
+    <t>0.9922,0.0004,0.0018,0.0024</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.1359,0.9842,0.0010</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0570,0.0047,0.9140,0.0009</t>
-  </si>
-  <si>
-    <t>0.1023,0.0036,0.9072,0.0003</t>
-  </si>
-  <si>
-    <t>0.0042,0.0010,0.9909,0.0010</t>
-  </si>
-  <si>
-    <t>0.0209,0.0860,0.8348,0.0012</t>
-  </si>
-  <si>
-    <t>0.0032,0.6079,0.4242,0.0008</t>
-  </si>
-  <si>
-    <t>0.0045,0.0077,0.9921,0.0004</t>
-  </si>
-  <si>
-    <t>0.9676,0.0008,0.0240,0.0003</t>
-  </si>
-  <si>
-    <t>0.0192,0.0008,0.9778,0.0007</t>
-  </si>
-  <si>
-    <t>0.0088,0.9910,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9991,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.3585,0.7425,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9423,0.0706,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.6947,0.4300,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0024,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0000,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9700,0.0038,0.0053,0.0024</t>
-  </si>
-  <si>
-    <t>0.9705,0.0017,0.0173,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0004,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0832,0.0109,0.8683,0.0007</t>
-  </si>
-  <si>
-    <t>0.0070,0.0019,0.9923,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0003,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0101,0.9907,0.0011</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9889,0.0124,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0046,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0010,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9995,0.0010</t>
-  </si>
-  <si>
-    <t>0.4610,0.2590,0.0623,0.0006</t>
-  </si>
-  <si>
-    <t>0.9874,0.0013,0.0034,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.2911,0.9798,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0315,0.0037,0.9524,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9980,0.0008</t>
-  </si>
-  <si>
-    <t>0.0198,0.0043,0.9676,0.0008</t>
-  </si>
-  <si>
-    <t>0.9763,0.0013,0.0115,0.0002</t>
-  </si>
-  <si>
-    <t>0.9816,0.0000,0.0313,0.0001</t>
-  </si>
-  <si>
-    <t>0.9727,0.0081,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0026,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9946,0.0035,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0012,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0233,0.9915,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0064,0.9837,0.0009</t>
-  </si>
-  <si>
-    <t>0.0075,0.0148,0.9478,0.0026</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.6682,0.0001,0.2890,0.0050</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9982,0.0015</t>
-  </si>
-  <si>
-    <t>0.9915,0.0000,0.0005,0.0089</t>
-  </si>
-  <si>
-    <t>0.0058,0.0004,0.0000,0.9985</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0009,0.9980</t>
-  </si>
-  <si>
-    <t>0.9578,0.0006,0.0006,0.0217</t>
+    <t>0.0011,0.0007,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0018,0.9949,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.9617,0.0000,0.0593,0.0002</t>
+  </si>
+  <si>
+    <t>0.6907,0.0003,0.3651,0.0012</t>
+  </si>
+  <si>
+    <t>0.9899,0.0004,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0044,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9905,0.0080,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9835,0.0183,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0055,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0052,0.9863,0.0025</t>
+  </si>
+  <si>
+    <t>0.0004,0.0022,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0041,0.9946,0.0008</t>
+  </si>
+  <si>
+    <t>0.0096,0.0115,0.9711,0.0013</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.1130,0.0001,0.8775,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.0002,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9977,0.0015</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0353,0.0002,0.0000,0.9928</t>
+  </si>
+  <si>
+    <t>0.0093,0.0000,0.0000,0.9970</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0000,0.0006</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2060,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2088,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2116,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2144,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2158,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2172,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,7 +2186,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,7 +2200,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2214,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2242,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2241,7 +2256,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,7 +2284,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2298,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,7 +2326,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2325,7 +2340,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,10 +2351,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2353,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2381,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2424,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2437,7 +2452,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,7 +2494,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2508,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2507,7 +2522,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2550,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2549,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2592,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2606,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2620,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2634,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2801,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2830,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2829,7 +2844,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2858,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2872,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2886,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2899,7 +2914,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2928,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2942,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3064,7 +3079,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>346</v>
@@ -3151,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3179,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3221,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3235,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3249,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3277,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3291,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3305,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3319,7 +3334,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3333,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3431,7 +3446,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,7 +3460,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,7 +3474,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,7 +3488,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3487,7 +3502,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,7 +3516,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3515,7 +3530,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3529,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3543,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3572,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3568,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>373</v>
@@ -3627,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3655,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3683,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3725,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,10 +3751,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3750,10 +3765,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3782,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3796,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3820,10 +3835,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3837,7 +3852,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,7 +3866,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3879,7 +3894,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3908,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,7 +3922,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3950,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3964,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>377</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3963,7 +3978,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +3992,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,10 +4003,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4034,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,7 +4076,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,7 +4118,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>406</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4257,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,7 +4286,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,10 +4297,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4384,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4412,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4440,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4523,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4548,10 +4563,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4565,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4594,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,7 +4622,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,10 +4647,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4677,7 +4692,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4730,10 +4745,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>449</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>269</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>377</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +5014,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5098,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,7 +5112,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5153,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5167,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>475</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5252,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5266,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5280,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,10 +5319,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5349,7 +5364,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5378,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5392,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5419,7 +5434,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
